--- a/ba-kit/requirement-to-flow/sample/sample_basic_design.xlsx
+++ b/ba-kit/requirement-to-flow/sample/sample_basic_design.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -165,8 +165,19 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1F5C1F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -230,6 +241,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -885,7 +901,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1207,6 +1223,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="12" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="12" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="12" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15543,10 +15574,8 @@
       <c r="E10" s="31" t="n"/>
       <c r="F10" s="31" t="n"/>
       <c r="G10" s="31" t="n"/>
-      <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="H10" s="36" t="n">
+        <v>2</v>
       </c>
       <c r="I10" s="37" t="n"/>
       <c r="J10" s="37" t="n"/>
@@ -15656,10 +15685,8 @@
       <c r="E13" s="31" t="n"/>
       <c r="F13" s="31" t="n"/>
       <c r="G13" s="31" t="n"/>
-      <c r="H13" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="H13" s="36" t="n">
+        <v>5</v>
       </c>
       <c r="I13" s="37" t="n"/>
       <c r="J13" s="37" t="n"/>
@@ -15695,10 +15722,8 @@
       <c r="E14" s="31" t="n"/>
       <c r="F14" s="31" t="n"/>
       <c r="G14" s="31" t="n"/>
-      <c r="H14" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="H14" s="36" t="n">
+        <v>6</v>
       </c>
       <c r="I14" s="37" t="n"/>
       <c r="J14" s="37" t="n"/>
@@ -15735,7 +15760,7 @@
       <c r="F15" s="31" t="n"/>
       <c r="G15" s="31" t="n"/>
       <c r="H15" s="36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I15" s="37" t="n"/>
       <c r="J15" s="37" t="n"/>
@@ -15772,7 +15797,7 @@
       <c r="F16" s="31" t="n"/>
       <c r="G16" s="31" t="n"/>
       <c r="H16" s="36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I16" s="37" t="n"/>
       <c r="J16" s="37" t="n"/>
@@ -15808,10 +15833,8 @@
       <c r="E17" s="31" t="n"/>
       <c r="F17" s="31" t="n"/>
       <c r="G17" s="31" t="n"/>
-      <c r="H17" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="H17" s="36" t="n">
+        <v>9</v>
       </c>
       <c r="I17" s="37" t="n"/>
       <c r="J17" s="37" t="n"/>
@@ -15847,10 +15870,8 @@
       <c r="E18" s="31" t="n"/>
       <c r="F18" s="31" t="n"/>
       <c r="G18" s="31" t="n"/>
-      <c r="H18" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="H18" s="36" t="n">
+        <v>10</v>
       </c>
       <c r="I18" s="37" t="n"/>
       <c r="J18" s="37" t="n"/>
@@ -15887,7 +15908,7 @@
       <c r="F19" s="31" t="n"/>
       <c r="G19" s="31" t="n"/>
       <c r="H19" s="36" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I19" s="41" t="n"/>
       <c r="J19" s="41" t="n"/>
@@ -26512,23 +26533,71 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="64" t="n"/>
-      <c r="B10" s="67" t="n"/>
-      <c r="C10" s="65" t="n"/>
-      <c r="D10" s="65" t="n"/>
-      <c r="E10" s="65" t="n"/>
-      <c r="F10" s="65" t="n"/>
-      <c r="G10" s="65" t="n"/>
-      <c r="H10" s="65" t="n"/>
-      <c r="I10" s="65" t="n"/>
-      <c r="J10" s="65" t="n"/>
-      <c r="K10" s="75" t="n"/>
-      <c r="L10" s="75" t="n"/>
-      <c r="M10" s="65" t="n"/>
-      <c r="N10" s="65" t="n"/>
-      <c r="O10" s="67" t="n"/>
-      <c r="P10" s="65" t="n"/>
+    <row r="10" ht="30" customHeight="1" s="84">
+      <c r="A10" s="128" t="inlineStr">
+        <is>
+          <t>CHG-0005</t>
+        </is>
+      </c>
+      <c r="B10" s="129" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C10" s="130" t="inlineStr">
+        <is>
+          <t>BA Agent</t>
+        </is>
+      </c>
+      <c r="D10" s="130" t="inlineStr">
+        <is>
+          <t>MASTER_STANDARDIZATION</t>
+        </is>
+      </c>
+      <c r="E10" s="130" t="inlineStr"/>
+      <c r="F10" s="130" t="inlineStr"/>
+      <c r="G10" s="130" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="H10" s="130" t="inlineStr">
+        <is>
+          <t>Cot # rows 9-19</t>
+        </is>
+      </c>
+      <c r="I10" s="130" t="inlineStr">
+        <is>
+          <t>Danh lai so thu tu 1..11 (truoc do la 1,2,3,4,3,4,5,6,3,4,4 - loi co san trong template goc)</t>
+        </is>
+      </c>
+      <c r="J10" s="130" t="inlineStr">
+        <is>
+          <t>Feedback user 23/09/2026</t>
+        </is>
+      </c>
+      <c r="K10" s="131" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="L10" s="131" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M10" s="130" t="inlineStr">
+        <is>
+          <t>WAITING APPROVAL</t>
+        </is>
+      </c>
+      <c r="N10" s="130" t="inlineStr"/>
+      <c r="O10" s="132" t="inlineStr"/>
+      <c r="P10" s="130" t="inlineStr">
+        <is>
+          <t>Loi co san o ca Sample lan Login_Sample cua ban goc, khong phai do thay doi truoc do</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="64" t="n"/>
